--- a/docs/lightml/CRA_56_PROFILE_LEGAL_VALIDATION.xlsx
+++ b/docs/lightml/CRA_56_PROFILE_LEGAL_VALIDATION.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: UU 13/2003 Ketenagakerjaan applies for ID.)</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: UU 13/2003 Ketenagakerjaan applies for ID.)</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: )</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: )</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: )</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: )</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: )</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: )</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: )</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: )</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: )</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: UU 2/2017 Jasa Konstruksi applies for ID.)</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: UU 2/2017 Jasa Konstruksi applies for ID.)</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: )</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: )</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: OJK regulations apply for ID.)</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: OJK regulations apply for ID.)</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>Active profile in CRA system. Engineering validation completed. Legal reviewer sign-off pending. (Notes: Fallback profile.)</t>
+          <t>Active profile in CRA system. Engineering implementation available. Repository evidence reviewed. Formal legal validation pending. (Notes: Fallback profile.)</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
